--- a/data/trans_dic/P25C$pormicuenta_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,47; 96,27</t>
+          <t>86,15; 96,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,75; 99,27</t>
+          <t>92,0; 99,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,65; 96,4</t>
+          <t>88,43; 96,77</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,97; 99,24</t>
+          <t>88,25; 99,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,0; 94,82</t>
+          <t>85,42; 95,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,3; 98,8</t>
+          <t>88,88; 98,73</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,4; 91,8</t>
+          <t>80,95; 91,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,91; 94,61</t>
+          <t>83,22; 94,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,49; 91,74</t>
+          <t>83,88; 91,77</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,48; 92,77</t>
+          <t>84,03; 93,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,22; 90,93</t>
+          <t>82,2; 91,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,95; 91,36</t>
+          <t>84,91; 91,29</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,68; 97,0</t>
+          <t>88,66; 97,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,33; 92,45</t>
+          <t>87,16; 92,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,13; 95,92</t>
+          <t>89,04; 95,7</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97868; 110241</t>
+          <t>98657; 110602</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45125; 48825</t>
+          <t>45249; 48818</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>145112; 157808</t>
+          <t>144762; 158400</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>350936; 395914</t>
+          <t>352058; 395796</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70861; 79047</t>
+          <t>71213; 79493</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>430716; 476518</t>
+          <t>428688; 476199</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113678; 129803</t>
+          <t>114459; 129692</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62063; 70820</t>
+          <t>62290; 70954</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180532; 198378</t>
+          <t>181388; 198437</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>162533; 180632</t>
+          <t>163604; 181527</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>105628; 118246</t>
+          <t>106890; 118616</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275860; 296693</t>
+          <t>275752; 296451</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>753362; 824064</t>
+          <t>753183; 824349</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>294702; 311951</t>
+          <t>294116; 311532</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1058013; 1138617</t>
+          <t>1056936; 1136007</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$pormicuenta_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,15; 96,59</t>
+          <t>84,44; 96,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,0; 99,26</t>
+          <t>92,54; 99,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,43; 96,77</t>
+          <t>88,78; 96,61</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,25; 99,21</t>
+          <t>85,05; 94,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,42; 95,36</t>
+          <t>86,01; 95,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,88; 98,73</t>
+          <t>87,01; 94,01</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,95; 91,73</t>
+          <t>81,1; 91,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,22; 94,79</t>
+          <t>83,51; 95,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,88; 91,77</t>
+          <t>83,8; 91,41</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,03; 93,23</t>
+          <t>83,77; 92,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,2; 91,21</t>
+          <t>81,92; 91,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,91; 91,29</t>
+          <t>84,92; 91,22</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,66; 97,03</t>
+          <t>86,52; 91,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,16; 92,32</t>
+          <t>87,7; 92,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,04; 95,7</t>
+          <t>87,84; 91,47</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>105788</t>
+          <t>113074</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47658</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153446</t>
+          <t>164415</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98657; 110602</t>
+          <t>103717; 118047</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45249; 48818</t>
+          <t>48913; 52485</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>144762; 158400</t>
+          <t>155968; 169718</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>383048</t>
+          <t>154894</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76071</t>
+          <t>82421</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>459119</t>
+          <t>237315</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>352058; 395796</t>
+          <t>145442; 161696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71213; 79493</t>
+          <t>77465; 86193</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>428688; 476199</t>
+          <t>227159; 245428</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>122997</t>
+          <t>142603</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67420</t>
+          <t>75439</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>190417</t>
+          <t>218043</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>114459; 129692</t>
+          <t>133446; 151122</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62290; 70954</t>
+          <t>69819; 79542</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181388; 198437</t>
+          <t>207945; 226821</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>174205</t>
+          <t>180084</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>113045</t>
+          <t>120999</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287249</t>
+          <t>301083</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>163604; 181527</t>
+          <t>169095; 187608</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>106890; 118616</t>
+          <t>114165; 126834</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275752; 296451</t>
+          <t>289758; 311271</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>786038</t>
+          <t>590654</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>330202</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1090232</t>
+          <t>920856</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>753183; 824349</t>
+          <t>571253; 605462</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>294116; 311532</t>
+          <t>320890; 339402</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1056936; 1136007</t>
+          <t>901378; 938614</t>
         </is>
       </c>
     </row>
